--- a/artfynd/A 45714-2025 artfynd.xlsx
+++ b/artfynd/A 45714-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,6 +792,520 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>129583101</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Korpberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>443210</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6618711</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Brattfors</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Storblockig sluttning i granskog med asp och björk.</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>På block.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>På block.</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129583082</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Korpberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>443235</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6618732</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Brattfors</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Storblockig sluttning i granskog med asp och björk.</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129582986</v>
+      </c>
+      <c r="B5" t="n">
+        <v>80184</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Korpberget, Vrm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>443241</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6618744</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Brattfors</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Storblockig sluttning i granskog med asp och björk.</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Äldre asp.</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Populus tremula # Äldre asp.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129582972</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lungsnäs, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>443241</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6618768</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Brattfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:03</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Storblockig sluttning i granskog med asp och björk.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Emma Enfjäll</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 45714-2025 artfynd.xlsx
+++ b/artfynd/A 45714-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129583101</v>
       </c>
       <c r="B3" t="n">
-        <v>79130</v>
+        <v>79156</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>129583082</v>
       </c>
       <c r="B4" t="n">
-        <v>79130</v>
+        <v>79156</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>129582986</v>
       </c>
       <c r="B5" t="n">
-        <v>80184</v>
+        <v>80210</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>129582972</v>
       </c>
       <c r="B6" t="n">
-        <v>79130</v>
+        <v>79156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45714-2025 artfynd.xlsx
+++ b/artfynd/A 45714-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129583101</v>
       </c>
       <c r="B3" t="n">
-        <v>79156</v>
+        <v>79161</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>129583082</v>
       </c>
       <c r="B4" t="n">
-        <v>79156</v>
+        <v>79161</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>129582986</v>
       </c>
       <c r="B5" t="n">
-        <v>80210</v>
+        <v>80215</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>129582972</v>
       </c>
       <c r="B6" t="n">
-        <v>79156</v>
+        <v>79161</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45714-2025 artfynd.xlsx
+++ b/artfynd/A 45714-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129583101</v>
       </c>
       <c r="B3" t="n">
-        <v>79161</v>
+        <v>79162</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>129583082</v>
       </c>
       <c r="B4" t="n">
-        <v>79161</v>
+        <v>79162</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>129582986</v>
       </c>
       <c r="B5" t="n">
-        <v>80215</v>
+        <v>80216</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>129582972</v>
       </c>
       <c r="B6" t="n">
-        <v>79161</v>
+        <v>79162</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45714-2025 artfynd.xlsx
+++ b/artfynd/A 45714-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129583101</v>
       </c>
       <c r="B3" t="n">
-        <v>79162</v>
+        <v>79167</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>129583082</v>
       </c>
       <c r="B4" t="n">
-        <v>79162</v>
+        <v>79167</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>129582986</v>
       </c>
       <c r="B5" t="n">
-        <v>80216</v>
+        <v>80221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>129582972</v>
       </c>
       <c r="B6" t="n">
-        <v>79162</v>
+        <v>79167</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45714-2025 artfynd.xlsx
+++ b/artfynd/A 45714-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>129583101</v>
       </c>
       <c r="B3" t="n">
-        <v>79167</v>
+        <v>79170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>129583082</v>
       </c>
       <c r="B4" t="n">
-        <v>79167</v>
+        <v>79170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1050,7 +1050,7 @@
         <v>129582986</v>
       </c>
       <c r="B5" t="n">
-        <v>80221</v>
+        <v>80224</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1191,7 +1191,7 @@
         <v>129582972</v>
       </c>
       <c r="B6" t="n">
-        <v>79167</v>
+        <v>79170</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 45714-2025 artfynd.xlsx
+++ b/artfynd/A 45714-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118293880</v>
+        <v>129582972</v>
       </c>
       <c r="B2" t="n">
-        <v>101237</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,49 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221343</v>
+        <v>6450</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Norstorp, vägrenen, Vrm</t>
+          <t>Lungsnäs, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>443317</v>
+        <v>443241</v>
       </c>
       <c r="R2" t="n">
-        <v>6618634</v>
+        <v>6618768</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,17 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-05</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Växte längs vägrenen under långa sträckor, antal 50 är en underskattning från ett bilstopp, men brunklöver förekom kontinuerligt längs vägen, skådad från bilen.</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,29 +771,39 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Blandskog i branter</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Storblockig sluttning i granskog med asp och björk.</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Stina Eriksson</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Stina Eriksson</t>
+          <t>Emma Enfjäll</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129583101</v>
+        <v>129583082</v>
       </c>
       <c r="B3" t="n">
-        <v>79173</v>
+        <v>79413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -833,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>443210</v>
+        <v>443235</v>
       </c>
       <c r="R3" t="n">
-        <v>6618711</v>
+        <v>6618732</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -899,16 +900,6 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Storblockig sluttning i granskog med asp och björk.</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>På block.</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>På block.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -926,14 +917,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129583082</v>
+        <v>129583101</v>
       </c>
       <c r="B4" t="n">
-        <v>79173</v>
+        <v>79413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -964,10 +955,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>443235</v>
+        <v>443210</v>
       </c>
       <c r="R4" t="n">
-        <v>6618732</v>
+        <v>6618711</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1030,6 +1021,16 @@
       <c r="AI4" t="inlineStr">
         <is>
           <t>Storblockig sluttning i granskog med asp och björk.</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>På block.</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>På block.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1050,7 +1051,7 @@
         <v>129582986</v>
       </c>
       <c r="B5" t="n">
-        <v>80227</v>
+        <v>80467</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1188,51 +1189,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129582972</v>
+        <v>118293880</v>
       </c>
       <c r="B6" t="n">
-        <v>79173</v>
+        <v>102464</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6450</v>
+        <v>221343</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skuggblåslav</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hypogymnia vittata</t>
+          <t>Trifolium spadiceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Parrique</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lungsnäs, Vrm</t>
+          <t>Norstorp, vägrenen, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>443241</v>
+        <v>443317</v>
       </c>
       <c r="R6" t="n">
-        <v>6618768</v>
+        <v>6618634</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1256,22 +1266,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2024-07-05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>14:03</t>
+          <t>2024-07-05</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Växte längs vägrenen under långa sträckor, antal 50 är en underskattning från ett bilstopp, men brunklöver förekom kontinuerligt längs vägen, skådad från bilen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1284,25 +1289,15 @@
       <c r="AG6" t="b">
         <v>0</v>
       </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Blandskog i branter</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Storblockig sluttning i granskog med asp och björk.</t>
-        </is>
-      </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
+          <t>Stina Eriksson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emma Enfjäll</t>
+          <t>Stina Eriksson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 45714-2025 artfynd.xlsx
+++ b/artfynd/A 45714-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129582972</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129583082</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1045,6 +1060,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129583101</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1186,6 +1206,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129582986</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1301,8 +1326,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118293880</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>